--- a/Automation_jobs_Report.xlsx
+++ b/Automation_jobs_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rajesh.jonnagaddla/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9370B9F2-36DB-E44B-9067-4F5FB147630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D98938-811F-2C46-865D-C96BF9DCD49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="31300" windowHeight="18380" xr2:uid="{5D965978-2E22-3A42-88C9-2DC2F6F20526}"/>
+    <workbookView xWindow="3260" yWindow="2260" windowWidth="31300" windowHeight="18380" activeTab="2" xr2:uid="{5D965978-2E22-3A42-88C9-2DC2F6F20526}"/>
   </bookViews>
   <sheets>
     <sheet name="Smart Sheet CSP" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>OF-24704</t>
   </si>
@@ -74,13 +74,52 @@
   </si>
   <si>
     <t>Make the change from testcase and validate. ${sheet_id}=         Set Variable    ${sheet_details}[1][${SERVICE}][result][id]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share file CSP All passed </t>
+  </si>
+  <si>
+    <t>OF-6175</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>http://opensearch.shared.int.shn.io/goto/2fe21607a4bbee811634b20008d7eade?security_tenant=global</t>
+  </si>
+  <si>
+    <t>No match / policy incorrect</t>
+  </si>
+  <si>
+    <t>OF-9114</t>
+  </si>
+  <si>
+    <t>OF-7149</t>
+  </si>
+  <si>
+    <t>rerun worked</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>sleep time worked</t>
+  </si>
+  <si>
+    <t>Failing the test as keyword create_public_link failed</t>
+  </si>
+  <si>
+    <t>OF-7627</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,8 +146,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,6 +165,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -146,10 +199,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,8 +227,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -576,18 +646,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{178119F2-37D0-F54D-B1FE-5CB02DE5E5E6}">
-  <dimension ref="A1"/>
+  <dimension ref="D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{772F2900-407E-0147-9F3B-B995A5AEA3B8}">
-  <dimension ref="A1"/>
+  <dimension ref="E2:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="76" style="12" customWidth="1"/>
+    <col min="7" max="7" width="85.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="5:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{B1C9101C-8E38-744C-9475-0FD2E5AABDB9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>